--- a/resources/templates/standard/D1100-05.xlsx
+++ b/resources/templates/standard/D1100-05.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -803,7 +806,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
@@ -824,15 +829,15 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
@@ -871,7 +876,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -881,7 +886,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -901,11 +906,11 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -921,7 +926,7 @@
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
@@ -931,21 +936,21 @@
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -975,10 +980,10 @@
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
@@ -1008,10 +1013,10 @@
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
@@ -1041,10 +1046,10 @@
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
@@ -1074,10 +1079,10 @@
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
@@ -1107,10 +1112,10 @@
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -1140,10 +1145,10 @@
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -1173,10 +1178,10 @@
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
@@ -1204,14 +1209,14 @@
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
@@ -1241,10 +1246,10 @@
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
@@ -1274,10 +1279,10 @@
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
@@ -1307,10 +1312,10 @@
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
@@ -1340,10 +1345,10 @@
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="19"/>
@@ -1373,10 +1378,10 @@
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="19"/>
       <c r="F18" s="19"/>
@@ -1406,10 +1411,10 @@
       <c r="A19" s="18"/>
       <c r="B19" s="18"/>
       <c r="C19" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
@@ -1437,14 +1442,14 @@
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
@@ -1474,10 +1479,10 @@
       <c r="A21" s="20"/>
       <c r="B21" s="20"/>
       <c r="C21" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
@@ -1507,10 +1512,10 @@
       <c r="A22" s="20"/>
       <c r="B22" s="20"/>
       <c r="C22" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="19"/>
@@ -1540,10 +1545,10 @@
       <c r="A23" s="20"/>
       <c r="B23" s="20"/>
       <c r="C23" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
@@ -1573,10 +1578,10 @@
       <c r="A24" s="20"/>
       <c r="B24" s="20"/>
       <c r="C24" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
@@ -1606,10 +1611,10 @@
       <c r="A25" s="20"/>
       <c r="B25" s="20"/>
       <c r="C25" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -1639,10 +1644,10 @@
       <c r="A26" s="20"/>
       <c r="B26" s="20"/>
       <c r="C26" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
@@ -1670,14 +1675,14 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
@@ -1707,10 +1712,10 @@
       <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
@@ -1740,10 +1745,10 @@
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
@@ -1773,10 +1778,10 @@
       <c r="A30" s="18"/>
       <c r="B30" s="18"/>
       <c r="C30" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
@@ -1804,14 +1809,14 @@
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E31" s="19"/>
       <c r="F31" s="19"/>
@@ -1841,10 +1846,10 @@
       <c r="A32" s="20"/>
       <c r="B32" s="20"/>
       <c r="C32" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
@@ -1874,10 +1879,10 @@
       <c r="A33" s="20"/>
       <c r="B33" s="20"/>
       <c r="C33" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" s="19"/>
       <c r="F33" s="19"/>
@@ -1907,10 +1912,10 @@
       <c r="A34" s="20"/>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -1938,12 +1943,12 @@
     </row>
     <row r="35" ht="20.1" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
@@ -1956,12 +1961,12 @@
       <c r="M35" s="24"/>
       <c r="N35" s="24"/>
       <c r="O35" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P35" s="10"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S35" s="24"/>
       <c r="T35" s="24"/>
